--- a/REIT_Pairs_Analytics_2026-10-25.xlsx
+++ b/REIT_Pairs_Analytics_2026-10-25.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
-    <t xml:space="preserve">Report Created: October 25, 2026 07:30 AM   |   Last Data Point in Analysis: October 23, 2026</t>
+    <t xml:space="preserve">Report Created: October 25, 2026 04:21 PM   |   Last Data Point in Analysis: October 23, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Recommendation Changes  |  Week of: October 25, 2026</t>
